--- a/example/万卡-B300-Q3400-二层-IB/para.xlsx
+++ b/example/万卡-B300-Q3400-二层-IB/para.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,6 +443,420 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hostname.xlsx</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>设备表-参数网</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>赋值表</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hostname.xlsx</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>设备表-存储网</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>赋值表</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hostname.xlsx</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>设备表-业务网</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>赋值表</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hostname.xlsx</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>设备表-带外网</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>赋值表</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>connection.xlsx</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>终端连接表-参数网</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>赋值表</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>connection.xlsx</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>终端连接表-存储网</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>赋值表</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>connection.xlsx</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>终端连接表-业务网</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>赋值表</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>connection.xlsx</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>终端连接表-带外网</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>赋值表</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>connection.xlsx</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VLAN网关表-参数网</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>赋值表</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>connection.xlsx</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VLAN网关表-存储网</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>赋值表</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>connection.xlsx</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VLAN网关表-业务网</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>赋值表</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ipaddress.xlsx</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IP规划地址表-参数网</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>对称表</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ipaddress.xlsx</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IP规划地址表-存储网</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>对称表</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ipaddress.xlsx</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IP规划地址表-业务网</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>对称表</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ipaddress.xlsx</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>IP规划地址表-带外网</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>对称表</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ipaddress.xlsx</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>环回地址表</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>赋值表</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ipaddress.xlsx</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>网段规划表</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>参数表</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>parameter.xlsx</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>参数表</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>参数表</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
